--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219943</v>
+        <v>121219962</v>
       </c>
       <c r="B5" t="n">
-        <v>98093</v>
+        <v>4766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639766</v>
+        <v>639782</v>
       </c>
       <c r="R5" t="n">
-        <v>6720969</v>
+        <v>6720979</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219811</v>
+        <v>121219943</v>
       </c>
       <c r="B7" t="n">
-        <v>90687</v>
+        <v>98103</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,25 +1248,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639787</v>
+        <v>639766</v>
       </c>
       <c r="R7" t="n">
-        <v>6720999</v>
+        <v>6720969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121219962</v>
+        <v>121219823</v>
       </c>
       <c r="B8" t="n">
-        <v>4766</v>
+        <v>98059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639782</v>
+        <v>639787</v>
       </c>
       <c r="R8" t="n">
-        <v>6720979</v>
+        <v>6720999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121219823</v>
+        <v>121219811</v>
       </c>
       <c r="B9" t="n">
-        <v>98049</v>
+        <v>90697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,25 +1452,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219962</v>
+        <v>121219943</v>
       </c>
       <c r="B5" t="n">
-        <v>4766</v>
+        <v>98103</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639782</v>
+        <v>639766</v>
       </c>
       <c r="R5" t="n">
-        <v>6720979</v>
+        <v>6720969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219754</v>
+        <v>121219962</v>
       </c>
       <c r="B6" t="n">
-        <v>6263</v>
+        <v>4766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105336</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639789</v>
+        <v>639782</v>
       </c>
       <c r="R6" t="n">
-        <v>6721051</v>
+        <v>6720979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219943</v>
+        <v>121219754</v>
       </c>
       <c r="B7" t="n">
-        <v>98103</v>
+        <v>6263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>105336</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639766</v>
+        <v>639789</v>
       </c>
       <c r="R7" t="n">
-        <v>6720969</v>
+        <v>6721051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219943</v>
+        <v>121219811</v>
       </c>
       <c r="B5" t="n">
-        <v>98103</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639766</v>
+        <v>639787</v>
       </c>
       <c r="R5" t="n">
-        <v>6720969</v>
+        <v>6720999</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219962</v>
+        <v>121219754</v>
       </c>
       <c r="B6" t="n">
-        <v>4766</v>
+        <v>6263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>105336</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639782</v>
+        <v>639789</v>
       </c>
       <c r="R6" t="n">
-        <v>6720979</v>
+        <v>6721051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219754</v>
+        <v>121219943</v>
       </c>
       <c r="B7" t="n">
-        <v>6263</v>
+        <v>98116</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105336</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639789</v>
+        <v>639766</v>
       </c>
       <c r="R7" t="n">
-        <v>6721051</v>
+        <v>6720969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121219823</v>
+        <v>121219962</v>
       </c>
       <c r="B8" t="n">
-        <v>98059</v>
+        <v>4766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639787</v>
+        <v>639782</v>
       </c>
       <c r="R8" t="n">
-        <v>6720999</v>
+        <v>6720979</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121219811</v>
+        <v>121219823</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>98072</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,25 +1452,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121219811</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>121219943</v>
       </c>
       <c r="B7" t="n">
-        <v>98116</v>
+        <v>98117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>121219823</v>
       </c>
       <c r="B9" t="n">
-        <v>98072</v>
+        <v>98073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219811</v>
+        <v>121219823</v>
       </c>
       <c r="B5" t="n">
-        <v>90710</v>
+        <v>98076</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219754</v>
+        <v>121219962</v>
       </c>
       <c r="B6" t="n">
-        <v>6263</v>
+        <v>4769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105336</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639789</v>
+        <v>639782</v>
       </c>
       <c r="R6" t="n">
-        <v>6721051</v>
+        <v>6720979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219943</v>
+        <v>121219754</v>
       </c>
       <c r="B7" t="n">
-        <v>98117</v>
+        <v>6266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>105336</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639766</v>
+        <v>639789</v>
       </c>
       <c r="R7" t="n">
-        <v>6720969</v>
+        <v>6721051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121219962</v>
+        <v>121219811</v>
       </c>
       <c r="B8" t="n">
-        <v>4766</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,25 +1350,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639782</v>
+        <v>639787</v>
       </c>
       <c r="R8" t="n">
-        <v>6720979</v>
+        <v>6720999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121219823</v>
+        <v>121219943</v>
       </c>
       <c r="B9" t="n">
-        <v>98073</v>
+        <v>98120</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>639787</v>
+        <v>639766</v>
       </c>
       <c r="R9" t="n">
-        <v>6720999</v>
+        <v>6720969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219962</v>
+        <v>121219943</v>
       </c>
       <c r="B6" t="n">
-        <v>4769</v>
+        <v>98120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639782</v>
+        <v>639766</v>
       </c>
       <c r="R6" t="n">
-        <v>6720979</v>
+        <v>6720969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219754</v>
+        <v>121219962</v>
       </c>
       <c r="B7" t="n">
-        <v>6266</v>
+        <v>4769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105336</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639789</v>
+        <v>639782</v>
       </c>
       <c r="R7" t="n">
-        <v>6721051</v>
+        <v>6720979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121219943</v>
+        <v>121219754</v>
       </c>
       <c r="B9" t="n">
-        <v>98120</v>
+        <v>6266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>105336</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>639766</v>
+        <v>639789</v>
       </c>
       <c r="R9" t="n">
-        <v>6720969</v>
+        <v>6721051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219823</v>
+        <v>121219811</v>
       </c>
       <c r="B5" t="n">
-        <v>98076</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219943</v>
+        <v>121219754</v>
       </c>
       <c r="B6" t="n">
-        <v>98120</v>
+        <v>6266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>105336</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639766</v>
+        <v>639789</v>
       </c>
       <c r="R6" t="n">
-        <v>6720969</v>
+        <v>6721051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219962</v>
+        <v>121219943</v>
       </c>
       <c r="B7" t="n">
-        <v>4769</v>
+        <v>98126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639782</v>
+        <v>639766</v>
       </c>
       <c r="R7" t="n">
-        <v>6720979</v>
+        <v>6720969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121219811</v>
+        <v>121219962</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>4769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,25 +1350,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639787</v>
+        <v>639782</v>
       </c>
       <c r="R8" t="n">
-        <v>6720999</v>
+        <v>6720979</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121219754</v>
+        <v>121219823</v>
       </c>
       <c r="B9" t="n">
-        <v>6266</v>
+        <v>98082</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105336</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>639789</v>
+        <v>639787</v>
       </c>
       <c r="R9" t="n">
-        <v>6721051</v>
+        <v>6720999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219811</v>
+        <v>121219962</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>4769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639787</v>
+        <v>639782</v>
       </c>
       <c r="R5" t="n">
-        <v>6720999</v>
+        <v>6720979</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219754</v>
+        <v>121219943</v>
       </c>
       <c r="B6" t="n">
-        <v>6266</v>
+        <v>98127</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105336</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639789</v>
+        <v>639766</v>
       </c>
       <c r="R6" t="n">
-        <v>6721051</v>
+        <v>6720969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219943</v>
+        <v>121219811</v>
       </c>
       <c r="B7" t="n">
-        <v>98126</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,25 +1248,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639766</v>
+        <v>639787</v>
       </c>
       <c r="R7" t="n">
-        <v>6720969</v>
+        <v>6720999</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121219962</v>
+        <v>121219823</v>
       </c>
       <c r="B8" t="n">
-        <v>4769</v>
+        <v>98083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639782</v>
+        <v>639787</v>
       </c>
       <c r="R8" t="n">
-        <v>6720979</v>
+        <v>6720999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121219823</v>
+        <v>121219754</v>
       </c>
       <c r="B9" t="n">
-        <v>98082</v>
+        <v>6266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>105336</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>639787</v>
+        <v>639789</v>
       </c>
       <c r="R9" t="n">
-        <v>6720999</v>
+        <v>6721051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121219962</v>
+        <v>121219943</v>
       </c>
       <c r="B5" t="n">
-        <v>4769</v>
+        <v>98127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639782</v>
+        <v>639766</v>
       </c>
       <c r="R5" t="n">
-        <v>6720979</v>
+        <v>6720969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219943</v>
+        <v>121219811</v>
       </c>
       <c r="B6" t="n">
-        <v>98127</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,25 +1146,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639766</v>
+        <v>639787</v>
       </c>
       <c r="R6" t="n">
-        <v>6720969</v>
+        <v>6720999</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219811</v>
+        <v>121219962</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>4769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,25 +1248,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639787</v>
+        <v>639782</v>
       </c>
       <c r="R7" t="n">
-        <v>6720999</v>
+        <v>6720979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121219811</v>
+        <v>121219962</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>4769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,25 +1146,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639787</v>
+        <v>639782</v>
       </c>
       <c r="R6" t="n">
-        <v>6720999</v>
+        <v>6720979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121219962</v>
+        <v>121219823</v>
       </c>
       <c r="B7" t="n">
-        <v>4769</v>
+        <v>98083</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639782</v>
+        <v>639787</v>
       </c>
       <c r="R7" t="n">
-        <v>6720979</v>
+        <v>6720999</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121219823</v>
+        <v>121219754</v>
       </c>
       <c r="B8" t="n">
-        <v>98083</v>
+        <v>6266</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>105336</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639787</v>
+        <v>639789</v>
       </c>
       <c r="R8" t="n">
-        <v>6720999</v>
+        <v>6721051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121219754</v>
+        <v>121219811</v>
       </c>
       <c r="B9" t="n">
-        <v>6266</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,25 +1452,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105336</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>639789</v>
+        <v>639787</v>
       </c>
       <c r="R9" t="n">
-        <v>6721051</v>
+        <v>6720999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46275-2024 artfynd.xlsx
+++ b/artfynd/A 46275-2024 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>127158379</v>
       </c>
       <c r="B10" t="n">
-        <v>90722</v>
+        <v>90796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
